--- a/Data/EC/NIT-9009368860.xlsx
+++ b/Data/EC/NIT-9009368860.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72835CF3-7608-48E5-B26D-49E131009D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{20A84E81-4184-470D-B4E5-0A846D310FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{046A9226-D30F-41E4-ABE1-B74B2ECFD53A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D6D4C7DD-7186-4D74-A241-73918BA21DE0}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="65">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -71,127 +71,133 @@
     <t>OTTO MARIO OSPINA BERRIO</t>
   </si>
   <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1908</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>1906</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1904</t>
+  </si>
+  <si>
+    <t>1903</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1901</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>1712</t>
+  </si>
+  <si>
+    <t>1711</t>
+  </si>
+  <si>
+    <t>1710</t>
+  </si>
+  <si>
+    <t>1709</t>
+  </si>
+  <si>
+    <t>1708</t>
+  </si>
+  <si>
+    <t>1707</t>
+  </si>
+  <si>
+    <t>1706</t>
+  </si>
+  <si>
     <t>1705</t>
   </si>
   <si>
-    <t>1706</t>
-  </si>
-  <si>
-    <t>1707</t>
-  </si>
-  <si>
-    <t>1708</t>
-  </si>
-  <si>
-    <t>1709</t>
-  </si>
-  <si>
-    <t>1710</t>
-  </si>
-  <si>
-    <t>1711</t>
-  </si>
-  <si>
-    <t>1712</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>1905</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>1907</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1909</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
+    <t>1047377698</t>
+  </si>
+  <si>
+    <t>JAIME ALFONSO HOLLMAN GONZALEZ</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -235,7 +241,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -290,9 +296,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -305,7 +309,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -505,23 +511,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -549,10 +555,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -590,22 +596,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>426600</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>189350</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD94A90E-4C2F-C6D8-0F4B-31AAC5F9FFB6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFCBFCA6-8C00-6BA2-C9BA-426DBAB604A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -627,7 +633,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="680600" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -956,27 +962,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D271C515-B26F-48F6-B0E8-67B2631E5042}">
-  <dimension ref="B2:J62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0C31DE1-A058-4830-A00C-663F6A3DEEEA}">
+  <dimension ref="B2:J65"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="16.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -985,7 +991,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -996,7 +1002,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1007,7 +1013,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1018,10 +1024,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1"/>
-    <row r="7" spans="2:10">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1034,8 +1040,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1"/>
-    <row r="9" spans="2:10">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1050,15 +1056,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1"/>
-    <row r="11" spans="2:10">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>1128860</v>
+        <v>1218936</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1066,17 +1072,17 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1"/>
-    <row r="13" spans="2:10">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C13" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F13" s="5">
         <v>41</v>
@@ -1086,7 +1092,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1106,16 +1112,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1129,7 +1135,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="18">
-        <v>27578</v>
+        <v>25740</v>
       </c>
       <c r="G16" s="18">
         <v>689455</v>
@@ -1138,7 +1144,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1161,7 +1167,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1184,7 +1190,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1207,7 +1213,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1230,7 +1236,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1253,7 +1259,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1276,7 +1282,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1299,7 +1305,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1322,7 +1328,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1345,7 +1351,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1368,7 +1374,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1391,7 +1397,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1414,7 +1420,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1437,7 +1443,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1460,7 +1466,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1483,7 +1489,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1506,7 +1512,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1529,7 +1535,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1552,7 +1558,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1575,7 +1581,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1598,7 +1604,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1621,7 +1627,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1644,7 +1650,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1667,7 +1673,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1690,7 +1696,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1713,7 +1719,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1736,7 +1742,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1759,7 +1765,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1782,7 +1788,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1805,7 +1811,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1828,7 +1834,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1851,7 +1857,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1874,7 +1880,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1897,7 +1903,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -1920,7 +1926,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -1943,7 +1949,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -1966,7 +1972,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -1989,7 +1995,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2012,7 +2018,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2035,57 +2041,126 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10">
-      <c r="B56" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E56" s="22" t="s">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B56" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="F56" s="24">
-        <v>25740</v>
-      </c>
-      <c r="G56" s="24">
-        <v>689455</v>
-      </c>
-      <c r="H56" s="25"/>
-      <c r="I56" s="25"/>
-      <c r="J56" s="26"/>
-    </row>
-    <row r="61" spans="2:10">
-      <c r="B61" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="C61" s="32"/>
-      <c r="H61" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-    </row>
-    <row r="62" spans="2:10">
-      <c r="B62" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="C62" s="32"/>
-      <c r="H62" s="1" t="s">
+      <c r="F56" s="18">
+        <v>27578</v>
+      </c>
+      <c r="G56" s="18">
+        <v>689455</v>
+      </c>
+      <c r="H56" s="19"/>
+      <c r="I56" s="19"/>
+      <c r="J56" s="20"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B57" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E57" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F57" s="18">
+        <v>31249</v>
+      </c>
+      <c r="G57" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H57" s="19"/>
+      <c r="I57" s="19"/>
+      <c r="J57" s="20"/>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B58" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D58" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E58" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F58" s="18">
+        <v>31249</v>
+      </c>
+      <c r="G58" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H58" s="19"/>
+      <c r="I58" s="19"/>
+      <c r="J58" s="20"/>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B59" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D59" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="E59" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="F59" s="24">
+        <v>27578</v>
+      </c>
+      <c r="G59" s="24">
+        <v>781242</v>
+      </c>
+      <c r="H59" s="25"/>
+      <c r="I59" s="25"/>
+      <c r="J59" s="26"/>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B64" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C64" s="32"/>
+      <c r="H64" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B65" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
+      <c r="C65" s="32"/>
+      <c r="H65" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="H65:J65"/>
+    <mergeCell ref="H64:J64"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
